--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t>tired after last class</t>
+  </si>
+  <si>
+    <t>practiced python</t>
   </si>
 </sst>
 </file>
@@ -1705,26 +1708,50 @@
       </c>
     </row>
     <row r="20" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A20" s="18"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="17"/>
+      <c r="A20" s="18">
+        <v>46277</v>
+      </c>
+      <c r="B20" s="19">
+        <v>420</v>
+      </c>
+      <c r="C20" s="19">
+        <v>30</v>
+      </c>
+      <c r="D20" s="19">
+        <v>90</v>
+      </c>
+      <c r="E20" s="19">
+        <v>15</v>
+      </c>
+      <c r="F20" s="19">
+        <v>0</v>
+      </c>
+      <c r="G20" s="19">
+        <v>0</v>
+      </c>
+      <c r="H20" s="19">
+        <v>50</v>
+      </c>
+      <c r="I20" s="15">
+        <f t="shared" si="0"/>
+        <v>605</v>
+      </c>
+      <c r="J20" s="15">
+        <f t="shared" si="1"/>
+        <v>835</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="21" spans="1:14" ht="14.25" customHeight="1">
       <c r="A21" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -243,6 +243,9 @@
   </si>
   <si>
     <t>practiced python</t>
+  </si>
+  <si>
+    <t>I've 5 CA1 next week</t>
   </si>
 </sst>
 </file>
@@ -1754,26 +1757,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="17"/>
+      <c r="A21" s="18">
+        <v>46278</v>
+      </c>
+      <c r="B21" s="19">
+        <v>415</v>
+      </c>
+      <c r="C21" s="19">
+        <v>20</v>
+      </c>
+      <c r="D21" s="19">
+        <v>150</v>
+      </c>
+      <c r="E21" s="19">
+        <v>20</v>
+      </c>
+      <c r="F21" s="19">
+        <v>0</v>
+      </c>
+      <c r="G21" s="19">
+        <v>0</v>
+      </c>
+      <c r="H21" s="19">
+        <v>70</v>
+      </c>
+      <c r="I21" s="15">
+        <f t="shared" si="0"/>
+        <v>675</v>
+      </c>
+      <c r="J21" s="15">
+        <f t="shared" si="1"/>
+        <v>765</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L21" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M21" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="22" spans="1:14" ht="14.25" customHeight="1">
       <c r="A22" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>I've 5 CA1 next week</t>
+  </si>
+  <si>
+    <t>prepared for CA1 of python</t>
   </si>
 </sst>
 </file>
@@ -1803,26 +1806,50 @@
       </c>
     </row>
     <row r="22" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A22" s="18"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="17"/>
+      <c r="A22" s="18">
+        <v>46279</v>
+      </c>
+      <c r="B22" s="19">
+        <v>450</v>
+      </c>
+      <c r="C22" s="19">
+        <v>30</v>
+      </c>
+      <c r="D22" s="19">
+        <v>120</v>
+      </c>
+      <c r="E22" s="19">
+        <v>30</v>
+      </c>
+      <c r="F22" s="19">
+        <v>200</v>
+      </c>
+      <c r="G22" s="19">
+        <v>4</v>
+      </c>
+      <c r="H22" s="19">
+        <v>60</v>
+      </c>
+      <c r="I22" s="15">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J22" s="15">
+        <f t="shared" si="1"/>
+        <v>550</v>
+      </c>
+      <c r="K22" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M22" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="23" spans="1:14" ht="14.25" customHeight="1">
       <c r="A23" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>prepared for CA1 of python</t>
+  </si>
+  <si>
+    <t>it was worst exam of my life CA1 python</t>
   </si>
 </sst>
 </file>
@@ -1852,26 +1855,50 @@
       </c>
     </row>
     <row r="23" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="17"/>
+      <c r="A23" s="18">
+        <v>46280</v>
+      </c>
+      <c r="B23" s="19">
+        <v>420</v>
+      </c>
+      <c r="C23" s="19">
+        <v>30</v>
+      </c>
+      <c r="D23" s="19">
+        <v>90</v>
+      </c>
+      <c r="E23" s="19">
+        <v>20</v>
+      </c>
+      <c r="F23" s="19">
+        <v>300</v>
+      </c>
+      <c r="G23" s="19">
+        <v>6</v>
+      </c>
+      <c r="H23" s="19">
+        <v>120</v>
+      </c>
+      <c r="I23" s="15">
+        <f t="shared" si="0"/>
+        <v>980</v>
+      </c>
+      <c r="J23" s="15">
+        <f t="shared" si="1"/>
+        <v>460</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L23" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M23" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="24" spans="1:14" ht="14.25" customHeight="1">
       <c r="A24" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -252,6 +252,9 @@
   </si>
   <si>
     <t>it was worst exam of my life CA1 python</t>
+  </si>
+  <si>
+    <t>I got 41 out of 50 in python CA1</t>
   </si>
 </sst>
 </file>
@@ -1901,26 +1904,50 @@
       </c>
     </row>
     <row r="24" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="17"/>
+      <c r="A24" s="18">
+        <v>46281</v>
+      </c>
+      <c r="B24" s="19">
+        <v>460</v>
+      </c>
+      <c r="C24" s="19">
+        <v>0</v>
+      </c>
+      <c r="D24" s="19">
+        <v>130</v>
+      </c>
+      <c r="E24" s="19">
+        <v>45</v>
+      </c>
+      <c r="F24" s="19">
+        <v>150</v>
+      </c>
+      <c r="G24" s="19">
+        <v>3</v>
+      </c>
+      <c r="H24" s="19">
+        <v>120</v>
+      </c>
+      <c r="I24" s="15">
+        <f t="shared" si="0"/>
+        <v>905</v>
+      </c>
+      <c r="J24" s="15">
+        <f t="shared" si="1"/>
+        <v>535</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="25" spans="1:14" ht="14.25" customHeight="1">
       <c r="A25" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -255,6 +255,12 @@
   </si>
   <si>
     <t>I got 41 out of 50 in python CA1</t>
+  </si>
+  <si>
+    <t>17-09-2026</t>
+  </si>
+  <si>
+    <t>today was CA1 of DBMS</t>
   </si>
 </sst>
 </file>
@@ -1950,26 +1956,50 @@
       </c>
     </row>
     <row r="25" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A25" s="18"/>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="17"/>
+      <c r="A25" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="19">
+        <v>430</v>
+      </c>
+      <c r="C25" s="19">
+        <v>50</v>
+      </c>
+      <c r="D25" s="19">
+        <v>120</v>
+      </c>
+      <c r="E25" s="19">
+        <v>20</v>
+      </c>
+      <c r="F25" s="19">
+        <v>250</v>
+      </c>
+      <c r="G25" s="19">
+        <v>5</v>
+      </c>
+      <c r="H25" s="19">
+        <v>90</v>
+      </c>
+      <c r="I25" s="15">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J25" s="15">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L25" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M25" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="26" spans="1:14" ht="14.25" customHeight="1">
       <c r="A26" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,10 +257,10 @@
     <t>I got 41 out of 50 in python CA1</t>
   </si>
   <si>
-    <t>17-09-2026</t>
+    <t>today was CA1 of DBMS</t>
   </si>
   <si>
-    <t>today was CA1 of DBMS</t>
+    <t>it was a good day</t>
   </si>
 </sst>
 </file>
@@ -1956,8 +1956,8 @@
       </c>
     </row>
     <row r="25" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A25" s="18" t="s">
-        <v>80</v>
+      <c r="A25" s="18">
+        <v>46282</v>
       </c>
       <c r="B25" s="19">
         <v>430</v>
@@ -1998,30 +1998,54 @@
         <v>55</v>
       </c>
       <c r="N25" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="14.25" customHeight="1">
+      <c r="A26" s="18">
+        <v>46284</v>
+      </c>
+      <c r="B26" s="19">
+        <v>440</v>
+      </c>
+      <c r="C26" s="19">
+        <v>30</v>
+      </c>
+      <c r="D26" s="19">
+        <v>120</v>
+      </c>
+      <c r="E26" s="19">
+        <v>20</v>
+      </c>
+      <c r="F26" s="19">
+        <v>0</v>
+      </c>
+      <c r="G26" s="19">
+        <v>0</v>
+      </c>
+      <c r="H26" s="19">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="J26" s="15">
+        <f t="shared" si="1"/>
+        <v>770</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L26" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M26" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N26" s="17" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A26" s="18"/>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" ht="14.25" customHeight="1">
       <c r="A27" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>it was a good day</t>
+  </si>
+  <si>
+    <t>studied for DBMS viva and mid terms</t>
   </si>
 </sst>
 </file>
@@ -2048,26 +2051,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A27" s="18"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="17"/>
+      <c r="A27" s="18">
+        <v>46285</v>
+      </c>
+      <c r="B27" s="19">
+        <v>470</v>
+      </c>
+      <c r="C27" s="19">
+        <v>45</v>
+      </c>
+      <c r="D27" s="19">
+        <v>90</v>
+      </c>
+      <c r="E27" s="19">
+        <v>30</v>
+      </c>
+      <c r="F27" s="19">
+        <v>0</v>
+      </c>
+      <c r="G27" s="19">
+        <v>0</v>
+      </c>
+      <c r="H27" s="19">
+        <v>60</v>
+      </c>
+      <c r="I27" s="15">
+        <f t="shared" si="0"/>
+        <v>695</v>
+      </c>
+      <c r="J27" s="15">
+        <f t="shared" si="1"/>
+        <v>745</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L27" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="28" spans="1:14" ht="14.25" customHeight="1">
       <c r="A28" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>studied for DBMS viva and mid terms</t>
+  </si>
+  <si>
+    <t>Felt a bit tired after evening class.</t>
   </si>
 </sst>
 </file>
@@ -2097,26 +2100,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A28" s="18"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="17"/>
+      <c r="A28" s="18">
+        <v>46286</v>
+      </c>
+      <c r="B28" s="19">
+        <v>430</v>
+      </c>
+      <c r="C28" s="19">
+        <v>20</v>
+      </c>
+      <c r="D28" s="19">
+        <v>45</v>
+      </c>
+      <c r="E28" s="19">
+        <v>20</v>
+      </c>
+      <c r="F28" s="19">
+        <v>250</v>
+      </c>
+      <c r="G28" s="19">
+        <v>5</v>
+      </c>
+      <c r="H28" s="19">
+        <v>60</v>
+      </c>
+      <c r="I28" s="15">
+        <f t="shared" si="0"/>
+        <v>825</v>
+      </c>
+      <c r="J28" s="15">
+        <f t="shared" si="1"/>
+        <v>615</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="29" spans="1:14" ht="14.25" customHeight="1">
       <c r="A29" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>Felt a bit tired after evening class.</t>
+  </si>
+  <si>
+    <t>Gave viva for CA1</t>
   </si>
 </sst>
 </file>
@@ -2146,26 +2149,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A29" s="18"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="20"/>
-      <c r="N29" s="17"/>
+      <c r="A29" s="18">
+        <v>46287</v>
+      </c>
+      <c r="B29" s="19">
+        <v>460</v>
+      </c>
+      <c r="C29" s="19">
+        <v>0</v>
+      </c>
+      <c r="D29" s="19">
+        <v>120</v>
+      </c>
+      <c r="E29" s="19">
+        <v>90</v>
+      </c>
+      <c r="F29" s="19">
+        <v>300</v>
+      </c>
+      <c r="G29" s="19">
+        <v>6</v>
+      </c>
+      <c r="H29" s="19">
+        <v>45</v>
+      </c>
+      <c r="I29" s="15">
+        <f t="shared" si="0"/>
+        <v>1015</v>
+      </c>
+      <c r="J29" s="15">
+        <f t="shared" si="1"/>
+        <v>425</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L29" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="30" spans="1:14" ht="14.25" customHeight="1">
       <c r="A30" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>Gave viva for CA1</t>
+  </si>
+  <si>
+    <t>preaparing for CA2</t>
   </si>
 </sst>
 </file>
@@ -2195,26 +2198,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A30" s="18"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="20"/>
-      <c r="N30" s="17"/>
+      <c r="A30" s="18">
+        <v>46288</v>
+      </c>
+      <c r="B30" s="19">
+        <v>420</v>
+      </c>
+      <c r="C30" s="19">
+        <v>0</v>
+      </c>
+      <c r="D30" s="19">
+        <v>110</v>
+      </c>
+      <c r="E30" s="19">
+        <v>20</v>
+      </c>
+      <c r="F30" s="19">
+        <v>200</v>
+      </c>
+      <c r="G30" s="19">
+        <v>4</v>
+      </c>
+      <c r="H30" s="19">
+        <v>60</v>
+      </c>
+      <c r="I30" s="15">
+        <f t="shared" si="0"/>
+        <v>810</v>
+      </c>
+      <c r="J30" s="15">
+        <f t="shared" si="1"/>
+        <v>630</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="L30" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M30" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="31" spans="1:14" ht="14.25" customHeight="1">
       <c r="A31" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -967,7 +967,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:O401"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -981,7 +981,7 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1">
+    <row r="1" spans="1:15" ht="21.75" customHeight="1">
       <c r="A1" s="23" t="s">
         <v>30</v>
       </c>
@@ -999,7 +999,7 @@
       <c r="M1" s="22"/>
       <c r="N1" s="22"/>
     </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1">
+    <row r="2" spans="1:15" ht="19.5" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>31</v>
       </c>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G2" s="26"/>
     </row>
-    <row r="3" spans="1:14" ht="19.5" customHeight="1">
+    <row r="3" spans="1:15" ht="19.5" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>34</v>
       </c>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="G3" s="26"/>
     </row>
-    <row r="4" spans="1:14" ht="14.25" customHeight="1">
+    <row r="4" spans="1:15" ht="14.25" customHeight="1">
       <c r="A4" s="21" t="s">
         <v>38</v>
       </c>
@@ -1051,7 +1051,7 @@
       <c r="M4" s="22"/>
       <c r="N4" s="22"/>
     </row>
-    <row r="5" spans="1:14" ht="14.25" customHeight="1">
+    <row r="5" spans="1:15" ht="14.25" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>39</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="14.25" customHeight="1">
+    <row r="6" spans="1:15" ht="14.25" customHeight="1">
       <c r="A6" s="8">
         <v>46223</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="14.25" customHeight="1">
+    <row r="7" spans="1:15" ht="14.25" customHeight="1">
       <c r="A7" s="13">
         <v>46259</v>
       </c>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="N7" s="17"/>
     </row>
-    <row r="8" spans="1:14" ht="14.25" customHeight="1">
+    <row r="8" spans="1:15" ht="14.25" customHeight="1">
       <c r="A8" s="18">
         <v>46261</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="14.25" customHeight="1">
+    <row r="9" spans="1:15" ht="14.25" customHeight="1">
       <c r="A9" s="18">
         <v>46262</v>
       </c>
@@ -1277,7 +1277,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="14.25" customHeight="1">
+    <row r="10" spans="1:15" ht="14.25" customHeight="1">
       <c r="A10" s="18">
         <v>46263</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="14.25" customHeight="1">
+    <row r="11" spans="1:15" ht="14.25" customHeight="1">
       <c r="A11" s="18">
         <v>46264</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="14.25" customHeight="1">
+    <row r="12" spans="1:15" ht="14.25" customHeight="1">
       <c r="A12" s="18">
         <v>46265</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="14.25" customHeight="1">
+    <row r="13" spans="1:15" ht="14.25" customHeight="1">
       <c r="A13" s="18">
         <v>46266</v>
       </c>
@@ -1460,8 +1460,9 @@
       <c r="N13" s="17" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" ht="14.25" customHeight="1">
+      <c r="O13" s="17"/>
+    </row>
+    <row r="14" spans="1:15" ht="14.25" customHeight="1">
       <c r="A14" s="18">
         <v>46267</v>
       </c>
@@ -1507,7 +1508,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="14.25" customHeight="1">
+    <row r="15" spans="1:15" ht="14.25" customHeight="1">
       <c r="A15" s="18">
         <v>46268</v>
       </c>
@@ -1553,7 +1554,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="14.25" customHeight="1">
+    <row r="16" spans="1:15" ht="14.25" customHeight="1">
       <c r="A16" s="18">
         <v>46269</v>
       </c>
@@ -2244,26 +2245,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A31" s="18"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="17"/>
+      <c r="A31" s="18">
+        <v>46289</v>
+      </c>
+      <c r="B31" s="19">
+        <v>440</v>
+      </c>
+      <c r="C31" s="19">
+        <v>25</v>
+      </c>
+      <c r="D31" s="19">
+        <v>90</v>
+      </c>
+      <c r="E31" s="19">
+        <v>10</v>
+      </c>
+      <c r="F31" s="19">
+        <v>250</v>
+      </c>
+      <c r="G31" s="19">
+        <v>5</v>
+      </c>
+      <c r="H31" s="19">
+        <v>120</v>
+      </c>
+      <c r="I31" s="15">
+        <f t="shared" si="0"/>
+        <v>935</v>
+      </c>
+      <c r="J31" s="15">
+        <f t="shared" si="1"/>
+        <v>505</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L31" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M31" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="32" spans="1:14" ht="14.25" customHeight="1">
       <c r="A32" s="18"/>
@@ -2307,7 +2332,6 @@
       <c r="K33" s="20"/>
       <c r="L33" s="20"/>
       <c r="M33" s="20"/>
-      <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" ht="14.25" customHeight="1">
       <c r="A34" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -273,6 +273,12 @@
   </si>
   <si>
     <t>preaparing for CA2</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Excellent</t>
   </si>
 </sst>
 </file>
@@ -2291,25 +2297,47 @@
       </c>
     </row>
     <row r="32" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A32" s="18"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="20"/>
+      <c r="A32" s="18">
+        <v>46290</v>
+      </c>
+      <c r="B32" s="19">
+        <v>430</v>
+      </c>
+      <c r="C32" s="19">
+        <v>0</v>
+      </c>
+      <c r="D32" s="19">
+        <v>120</v>
+      </c>
+      <c r="E32" s="19">
+        <v>30</v>
+      </c>
+      <c r="F32" s="19">
+        <v>200</v>
+      </c>
+      <c r="G32" s="19">
+        <v>4</v>
+      </c>
+      <c r="H32" s="19">
+        <v>120</v>
+      </c>
+      <c r="I32" s="15">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="J32" s="15">
+        <f t="shared" si="1"/>
+        <v>540</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>62</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" ht="14.25" customHeight="1">

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,6 +280,9 @@
   <si>
     <t>Excellent</t>
   </si>
+  <si>
+    <t>preparing for mid terms</t>
+  </si>
 </sst>
 </file>
 
@@ -390,7 +393,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -450,11 +453,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -514,6 +528,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2338,28 +2355,55 @@
       <c r="M32" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="N32" s="17"/>
+      <c r="N32" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="33" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A33" s="18"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="20"/>
+      <c r="A33" s="18">
+        <v>46291</v>
+      </c>
+      <c r="B33" s="19">
+        <v>460</v>
+      </c>
+      <c r="C33" s="19">
+        <v>20</v>
+      </c>
+      <c r="D33" s="19">
+        <v>180</v>
+      </c>
+      <c r="E33" s="19">
+        <v>45</v>
+      </c>
+      <c r="F33" s="19">
+        <v>0</v>
+      </c>
+      <c r="G33" s="19">
+        <v>0</v>
+      </c>
+      <c r="H33" s="19">
+        <v>120</v>
+      </c>
+      <c r="I33" s="15">
+        <f t="shared" si="0"/>
+        <v>825</v>
+      </c>
+      <c r="J33" s="15">
+        <f t="shared" si="1"/>
+        <v>615</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M33" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N33" s="29" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="34" spans="1:14" ht="14.25" customHeight="1">
       <c r="A34" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="90">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,9 @@
   <si>
     <t>preparing for mid terms</t>
   </si>
+  <si>
+    <t>college is suspended for 10 days</t>
+  </si>
 </sst>
 </file>
 
@@ -518,6 +521,9 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -528,9 +534,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1005,74 +1008,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="21.75" customHeight="1">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-      <c r="K1" s="22"/>
-      <c r="L1" s="22"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="22"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
     </row>
     <row r="2" spans="1:15" ht="19.5" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="27"/>
       <c r="E2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="28">
         <v>12622534</v>
       </c>
-      <c r="G2" s="26"/>
+      <c r="G2" s="27"/>
     </row>
     <row r="3" spans="1:15" ht="19.5" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="27"/>
       <c r="E3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="26"/>
+      <c r="G3" s="27"/>
     </row>
     <row r="4" spans="1:15" ht="14.25" customHeight="1">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
     </row>
     <row r="5" spans="1:15" ht="14.25" customHeight="1">
       <c r="A5" s="7" t="s">
@@ -2401,31 +2404,55 @@
       <c r="M33" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="N33" s="29" t="s">
+      <c r="N33" s="21" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A34" s="18"/>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="20"/>
-      <c r="N34" s="17"/>
+      <c r="A34" s="18">
+        <v>46292</v>
+      </c>
+      <c r="B34" s="19">
+        <v>430</v>
+      </c>
+      <c r="C34" s="19">
+        <v>0</v>
+      </c>
+      <c r="D34" s="19">
+        <v>120</v>
+      </c>
+      <c r="E34" s="19">
+        <v>30</v>
+      </c>
+      <c r="F34" s="19">
+        <v>0</v>
+      </c>
+      <c r="G34" s="19">
+        <v>0</v>
+      </c>
+      <c r="H34" s="19">
+        <v>60</v>
+      </c>
+      <c r="I34" s="15">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J34" s="15">
+        <f t="shared" si="1"/>
+        <v>800</v>
+      </c>
+      <c r="K34" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L34" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M34" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="35" spans="1:14" ht="14.25" customHeight="1">
       <c r="A35" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>college is suspended for 10 days</t>
+  </si>
+  <si>
+    <t>today I submitted report file of python</t>
   </si>
 </sst>
 </file>
@@ -2455,26 +2458,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A35" s="18"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="20"/>
-      <c r="N35" s="17"/>
+      <c r="A35" s="18">
+        <v>46293</v>
+      </c>
+      <c r="B35" s="19">
+        <v>460</v>
+      </c>
+      <c r="C35" s="19">
+        <v>20</v>
+      </c>
+      <c r="D35" s="19">
+        <v>90</v>
+      </c>
+      <c r="E35" s="19">
+        <v>0</v>
+      </c>
+      <c r="F35" s="19">
+        <v>0</v>
+      </c>
+      <c r="G35" s="19">
+        <v>0</v>
+      </c>
+      <c r="H35" s="19">
+        <v>120</v>
+      </c>
+      <c r="I35" s="15">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J35" s="15">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
+      <c r="K35" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L35" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="M35" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="36" spans="1:14" ht="14.25" customHeight="1">
       <c r="A36" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -288,6 +288,9 @@
   </si>
   <si>
     <t>today I submitted report file of python</t>
+  </si>
+  <si>
+    <t>An easy day</t>
   </si>
 </sst>
 </file>
@@ -2504,26 +2507,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A36" s="18"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="20"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="20"/>
-      <c r="N36" s="17"/>
+      <c r="A36" s="18">
+        <v>46294</v>
+      </c>
+      <c r="B36" s="19">
+        <v>460</v>
+      </c>
+      <c r="C36" s="19">
+        <v>30</v>
+      </c>
+      <c r="D36" s="19">
+        <v>180</v>
+      </c>
+      <c r="E36" s="19">
+        <v>30</v>
+      </c>
+      <c r="F36" s="19">
+        <v>0</v>
+      </c>
+      <c r="G36" s="19">
+        <v>0</v>
+      </c>
+      <c r="H36" s="19">
+        <v>180</v>
+      </c>
+      <c r="I36" s="15">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J36" s="15">
+        <f t="shared" si="1"/>
+        <v>560</v>
+      </c>
+      <c r="K36" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L36" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M36" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="37" spans="1:14" ht="14.25" customHeight="1">
       <c r="A37" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -291,6 +291,9 @@
   </si>
   <si>
     <t>An easy day</t>
+  </si>
+  <si>
+    <t>Got new datesheet for MTT</t>
   </si>
 </sst>
 </file>
@@ -2553,26 +2556,50 @@
       </c>
     </row>
     <row r="37" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A37" s="18"/>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="20"/>
-      <c r="N37" s="17"/>
+      <c r="A37" s="18">
+        <v>46295</v>
+      </c>
+      <c r="B37" s="19">
+        <v>450</v>
+      </c>
+      <c r="C37" s="19">
+        <v>30</v>
+      </c>
+      <c r="D37" s="19">
+        <v>150</v>
+      </c>
+      <c r="E37" s="19">
+        <v>45</v>
+      </c>
+      <c r="F37" s="19">
+        <v>0</v>
+      </c>
+      <c r="G37" s="19">
+        <v>0</v>
+      </c>
+      <c r="H37" s="19">
+        <v>160</v>
+      </c>
+      <c r="I37" s="15">
+        <f t="shared" si="0"/>
+        <v>835</v>
+      </c>
+      <c r="J37" s="15">
+        <f t="shared" si="1"/>
+        <v>605</v>
+      </c>
+      <c r="K37" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M37" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="38" spans="1:14" ht="14.25" customHeight="1">
       <c r="A38" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="94">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -294,6 +294,9 @@
   </si>
   <si>
     <t>Got new datesheet for MTT</t>
+  </si>
+  <si>
+    <t>normal day</t>
   </si>
 </sst>
 </file>
@@ -2602,26 +2605,50 @@
       </c>
     </row>
     <row r="38" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A38" s="18"/>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="20"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="20"/>
-      <c r="N38" s="17"/>
+      <c r="A38" s="18">
+        <v>46296</v>
+      </c>
+      <c r="B38" s="19">
+        <v>500</v>
+      </c>
+      <c r="C38" s="19">
+        <v>60</v>
+      </c>
+      <c r="D38" s="19">
+        <v>120</v>
+      </c>
+      <c r="E38" s="19">
+        <v>0</v>
+      </c>
+      <c r="F38" s="19">
+        <v>0</v>
+      </c>
+      <c r="G38" s="19">
+        <v>0</v>
+      </c>
+      <c r="H38" s="19">
+        <v>120</v>
+      </c>
+      <c r="I38" s="15">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J38" s="15">
+        <f t="shared" si="1"/>
+        <v>640</v>
+      </c>
+      <c r="K38" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L38" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M38" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="39" spans="1:14" ht="14.25" customHeight="1">
       <c r="A39" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="95">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -297,6 +297,9 @@
   </si>
   <si>
     <t>normal day</t>
+  </si>
+  <si>
+    <t>The only easy day was yesterday</t>
   </si>
 </sst>
 </file>
@@ -2651,26 +2654,50 @@
       </c>
     </row>
     <row r="39" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A39" s="18"/>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="20"/>
-      <c r="L39" s="20"/>
-      <c r="M39" s="20"/>
-      <c r="N39" s="17"/>
+      <c r="A39" s="18">
+        <v>46297</v>
+      </c>
+      <c r="B39" s="19">
+        <v>420</v>
+      </c>
+      <c r="C39" s="19">
+        <v>30</v>
+      </c>
+      <c r="D39" s="19">
+        <v>180</v>
+      </c>
+      <c r="E39" s="19">
+        <v>20</v>
+      </c>
+      <c r="F39" s="19">
+        <v>0</v>
+      </c>
+      <c r="G39" s="19">
+        <v>0</v>
+      </c>
+      <c r="H39" s="19">
+        <v>110</v>
+      </c>
+      <c r="I39" s="15">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J39" s="15">
+        <f t="shared" si="1"/>
+        <v>680</v>
+      </c>
+      <c r="K39" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L39" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="40" spans="1:14" ht="14.25" customHeight="1">
       <c r="A40" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t>The only easy day was yesterday</t>
+  </si>
+  <si>
+    <t>India got 21 gold medals in asian games</t>
   </si>
 </sst>
 </file>
@@ -2700,26 +2703,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A40" s="18"/>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="20"/>
-      <c r="N40" s="17"/>
+      <c r="A40" s="18">
+        <v>46298</v>
+      </c>
+      <c r="B40" s="19">
+        <v>430</v>
+      </c>
+      <c r="C40" s="19">
+        <v>0</v>
+      </c>
+      <c r="D40" s="19">
+        <v>120</v>
+      </c>
+      <c r="E40" s="19">
+        <v>30</v>
+      </c>
+      <c r="F40" s="19">
+        <v>0</v>
+      </c>
+      <c r="G40" s="19">
+        <v>0</v>
+      </c>
+      <c r="H40" s="19">
+        <v>150</v>
+      </c>
+      <c r="I40" s="15">
+        <f t="shared" si="0"/>
+        <v>730</v>
+      </c>
+      <c r="J40" s="15">
+        <f t="shared" si="1"/>
+        <v>710</v>
+      </c>
+      <c r="K40" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="L40" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="M40" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="41" spans="1:14" ht="14.25" customHeight="1">
       <c r="A41" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -303,6 +303,9 @@
   </si>
   <si>
     <t>India got 21 gold medals in asian games</t>
+  </si>
+  <si>
+    <t>I've online class tomorrow</t>
   </si>
 </sst>
 </file>
@@ -2749,26 +2752,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A41" s="18"/>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="20"/>
-      <c r="N41" s="17"/>
+      <c r="A41" s="18">
+        <v>46299</v>
+      </c>
+      <c r="B41" s="19">
+        <v>450</v>
+      </c>
+      <c r="C41" s="19">
+        <v>25</v>
+      </c>
+      <c r="D41" s="19">
+        <v>150</v>
+      </c>
+      <c r="E41" s="19">
+        <v>0</v>
+      </c>
+      <c r="F41" s="19">
+        <v>0</v>
+      </c>
+      <c r="G41" s="19">
+        <v>0</v>
+      </c>
+      <c r="H41" s="19">
+        <v>130</v>
+      </c>
+      <c r="I41" s="15">
+        <f t="shared" si="0"/>
+        <v>755</v>
+      </c>
+      <c r="J41" s="15">
+        <f t="shared" si="1"/>
+        <v>685</v>
+      </c>
+      <c r="K41" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L41" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M41" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="42" spans="1:14" ht="14.25" customHeight="1">
       <c r="A42" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2798,26 +2798,50 @@
       </c>
     </row>
     <row r="42" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A42" s="18"/>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="17"/>
+      <c r="A42" s="18">
+        <v>46300</v>
+      </c>
+      <c r="B42" s="19">
+        <v>420</v>
+      </c>
+      <c r="C42" s="19">
+        <v>30</v>
+      </c>
+      <c r="D42" s="19">
+        <v>100</v>
+      </c>
+      <c r="E42" s="19">
+        <v>40</v>
+      </c>
+      <c r="F42" s="19">
+        <v>0</v>
+      </c>
+      <c r="G42" s="19">
+        <v>0</v>
+      </c>
+      <c r="H42" s="19">
+        <v>120</v>
+      </c>
+      <c r="I42" s="15">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="J42" s="15">
+        <f t="shared" si="1"/>
+        <v>730</v>
+      </c>
+      <c r="K42" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L42" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M42" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="43" spans="1:14" ht="14.25" customHeight="1">
       <c r="A43" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>I've online class tomorrow</t>
+  </si>
+  <si>
+    <t>just completed minor project 1</t>
   </si>
 </sst>
 </file>
@@ -2844,26 +2847,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A43" s="18"/>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="20"/>
-      <c r="N43" s="17"/>
+      <c r="A43" s="18">
+        <v>46301</v>
+      </c>
+      <c r="B43" s="19">
+        <v>450</v>
+      </c>
+      <c r="C43" s="19">
+        <v>0</v>
+      </c>
+      <c r="D43" s="19">
+        <v>120</v>
+      </c>
+      <c r="E43" s="19">
+        <v>20</v>
+      </c>
+      <c r="F43" s="19">
+        <v>250</v>
+      </c>
+      <c r="G43" s="19">
+        <v>5</v>
+      </c>
+      <c r="H43" s="19">
+        <v>120</v>
+      </c>
+      <c r="I43" s="15">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J43" s="15">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="K43" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L43" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M43" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="44" spans="1:14" ht="14.25" customHeight="1">
       <c r="A44" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2893,26 +2893,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A44" s="18"/>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="20"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="20"/>
-      <c r="N44" s="17"/>
+      <c r="A44" s="18">
+        <v>46302</v>
+      </c>
+      <c r="B44" s="19">
+        <v>410</v>
+      </c>
+      <c r="C44" s="19">
+        <v>0</v>
+      </c>
+      <c r="D44" s="19">
+        <v>250</v>
+      </c>
+      <c r="E44" s="19">
+        <v>0</v>
+      </c>
+      <c r="F44" s="19">
+        <v>300</v>
+      </c>
+      <c r="G44" s="19">
+        <v>6</v>
+      </c>
+      <c r="H44" s="19">
+        <v>45</v>
+      </c>
+      <c r="I44" s="15">
+        <f t="shared" si="0"/>
+        <v>1005</v>
+      </c>
+      <c r="J44" s="15">
+        <f t="shared" si="1"/>
+        <v>435</v>
+      </c>
+      <c r="K44" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L44" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M44" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="45" spans="1:14" ht="14.25" customHeight="1">
       <c r="A45" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2939,26 +2939,50 @@
       </c>
     </row>
     <row r="45" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A45" s="18"/>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="20"/>
-      <c r="N45" s="17"/>
+      <c r="A45" s="18">
+        <v>46274</v>
+      </c>
+      <c r="B45" s="19">
+        <v>450</v>
+      </c>
+      <c r="C45" s="19">
+        <v>20</v>
+      </c>
+      <c r="D45" s="19">
+        <v>120</v>
+      </c>
+      <c r="E45" s="19">
+        <v>0</v>
+      </c>
+      <c r="F45" s="19">
+        <v>0</v>
+      </c>
+      <c r="G45" s="19">
+        <v>0</v>
+      </c>
+      <c r="H45" s="19">
+        <v>160</v>
+      </c>
+      <c r="I45" s="15">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J45" s="15">
+        <f t="shared" si="1"/>
+        <v>690</v>
+      </c>
+      <c r="K45" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L45" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M45" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="46" spans="1:14" ht="14.25" customHeight="1">
       <c r="A46" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -2940,7 +2940,7 @@
     </row>
     <row r="45" spans="1:14" ht="14.25" customHeight="1">
       <c r="A45" s="18">
-        <v>46274</v>
+        <v>46304</v>
       </c>
       <c r="B45" s="19">
         <v>450</v>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>just completed minor project 1</t>
+  </si>
+  <si>
+    <t>stressed because of mid terms</t>
   </si>
 </sst>
 </file>
@@ -2985,26 +2988,50 @@
       </c>
     </row>
     <row r="46" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A46" s="18"/>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="20"/>
-      <c r="L46" s="20"/>
-      <c r="M46" s="20"/>
-      <c r="N46" s="17"/>
+      <c r="A46" s="18">
+        <v>46305</v>
+      </c>
+      <c r="B46" s="19">
+        <v>440</v>
+      </c>
+      <c r="C46" s="19">
+        <v>20</v>
+      </c>
+      <c r="D46" s="19">
+        <v>120</v>
+      </c>
+      <c r="E46" s="19">
+        <v>20</v>
+      </c>
+      <c r="F46" s="19">
+        <v>0</v>
+      </c>
+      <c r="G46" s="19">
+        <v>0</v>
+      </c>
+      <c r="H46" s="19">
+        <v>180</v>
+      </c>
+      <c r="I46" s="15">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J46" s="15">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="K46" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L46" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M46" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="47" spans="1:14" ht="14.25" customHeight="1">
       <c r="A47" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>stressed because of mid terms</t>
+  </si>
+  <si>
+    <t>just completed my syllabus</t>
   </si>
 </sst>
 </file>
@@ -3034,26 +3037,50 @@
       </c>
     </row>
     <row r="47" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A47" s="18"/>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="20"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="20"/>
-      <c r="N47" s="17"/>
+      <c r="A47" s="18">
+        <v>46306</v>
+      </c>
+      <c r="B47" s="19">
+        <v>400</v>
+      </c>
+      <c r="C47" s="19">
+        <v>0</v>
+      </c>
+      <c r="D47" s="19">
+        <v>200</v>
+      </c>
+      <c r="E47" s="19">
+        <v>0</v>
+      </c>
+      <c r="F47" s="19">
+        <v>0</v>
+      </c>
+      <c r="G47" s="19">
+        <v>0</v>
+      </c>
+      <c r="H47" s="19">
+        <v>120</v>
+      </c>
+      <c r="I47" s="15">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J47" s="15">
+        <f t="shared" si="1"/>
+        <v>720</v>
+      </c>
+      <c r="K47" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L47" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M47" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="48" spans="1:14" ht="14.25" customHeight="1">
       <c r="A48" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>just completed my syllabus</t>
+  </si>
+  <si>
+    <t>first mid term exam</t>
   </si>
 </sst>
 </file>
@@ -3083,26 +3086,50 @@
       </c>
     </row>
     <row r="48" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A48" s="18"/>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="20"/>
-      <c r="L48" s="20"/>
-      <c r="M48" s="20"/>
-      <c r="N48" s="17"/>
+      <c r="A48" s="18">
+        <v>46307</v>
+      </c>
+      <c r="B48" s="19">
+        <v>320</v>
+      </c>
+      <c r="C48" s="19">
+        <v>0</v>
+      </c>
+      <c r="D48" s="19">
+        <v>250</v>
+      </c>
+      <c r="E48" s="19">
+        <v>0</v>
+      </c>
+      <c r="F48" s="19">
+        <v>0</v>
+      </c>
+      <c r="G48" s="19">
+        <v>0</v>
+      </c>
+      <c r="H48" s="19">
+        <v>160</v>
+      </c>
+      <c r="I48" s="15">
+        <f t="shared" si="0"/>
+        <v>730</v>
+      </c>
+      <c r="J48" s="15">
+        <f t="shared" si="1"/>
+        <v>710</v>
+      </c>
+      <c r="K48" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L48" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M48" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="49" spans="1:14" ht="14.25" customHeight="1">
       <c r="A49" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t>first mid term exam</t>
+  </si>
+  <si>
+    <t>second mid term</t>
   </si>
 </sst>
 </file>
@@ -3132,26 +3135,50 @@
       </c>
     </row>
     <row r="49" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A49" s="18"/>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="20"/>
-      <c r="L49" s="20"/>
-      <c r="M49" s="20"/>
-      <c r="N49" s="17"/>
+      <c r="A49" s="18">
+        <v>46308</v>
+      </c>
+      <c r="B49" s="19">
+        <v>450</v>
+      </c>
+      <c r="C49" s="19">
+        <v>20</v>
+      </c>
+      <c r="D49" s="19">
+        <v>200</v>
+      </c>
+      <c r="E49" s="19">
+        <v>50</v>
+      </c>
+      <c r="F49" s="19">
+        <v>0</v>
+      </c>
+      <c r="G49" s="19">
+        <v>0</v>
+      </c>
+      <c r="H49" s="19">
+        <v>120</v>
+      </c>
+      <c r="I49" s="15">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J49" s="15">
+        <f t="shared" si="1"/>
+        <v>600</v>
+      </c>
+      <c r="K49" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L49" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M49" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="50" spans="1:14" ht="14.25" customHeight="1">
       <c r="A50" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -321,6 +321,9 @@
   </si>
   <si>
     <t>second mid term</t>
+  </si>
+  <si>
+    <t>third mid term</t>
   </si>
 </sst>
 </file>
@@ -3181,26 +3184,50 @@
       </c>
     </row>
     <row r="50" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A50" s="18"/>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="20"/>
-      <c r="L50" s="20"/>
-      <c r="M50" s="20"/>
-      <c r="N50" s="17"/>
+      <c r="A50" s="18">
+        <v>46309</v>
+      </c>
+      <c r="B50" s="19">
+        <v>500</v>
+      </c>
+      <c r="C50" s="19">
+        <v>20</v>
+      </c>
+      <c r="D50" s="19">
+        <v>150</v>
+      </c>
+      <c r="E50" s="19">
+        <v>0</v>
+      </c>
+      <c r="F50" s="19">
+        <v>0</v>
+      </c>
+      <c r="G50" s="19">
+        <v>0</v>
+      </c>
+      <c r="H50" s="19">
+        <v>180</v>
+      </c>
+      <c r="I50" s="15">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J50" s="15">
+        <f t="shared" si="1"/>
+        <v>590</v>
+      </c>
+      <c r="K50" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L50" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M50" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="51" spans="1:14" ht="14.25" customHeight="1">
       <c r="A51" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t>third mid term</t>
+  </si>
+  <si>
+    <t>second last mtt</t>
   </si>
 </sst>
 </file>
@@ -3230,26 +3233,50 @@
       </c>
     </row>
     <row r="51" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A51" s="18"/>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="20"/>
-      <c r="L51" s="20"/>
-      <c r="M51" s="20"/>
-      <c r="N51" s="17"/>
+      <c r="A51" s="18">
+        <v>46310</v>
+      </c>
+      <c r="B51" s="19">
+        <v>360</v>
+      </c>
+      <c r="C51" s="19">
+        <v>30</v>
+      </c>
+      <c r="D51" s="19">
+        <v>120</v>
+      </c>
+      <c r="E51" s="19">
+        <v>20</v>
+      </c>
+      <c r="F51" s="19">
+        <v>0</v>
+      </c>
+      <c r="G51" s="19">
+        <v>0</v>
+      </c>
+      <c r="H51" s="19">
+        <v>120</v>
+      </c>
+      <c r="I51" s="15">
+        <f t="shared" si="0"/>
+        <v>650</v>
+      </c>
+      <c r="J51" s="15">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="K51" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L51" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M51" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="52" spans="1:14" ht="14.25" customHeight="1">
       <c r="A52" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>second last mtt</t>
+  </si>
+  <si>
+    <t>prepraing for ett</t>
   </si>
 </sst>
 </file>
@@ -3279,26 +3282,50 @@
       </c>
     </row>
     <row r="52" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A52" s="18"/>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="20"/>
-      <c r="L52" s="20"/>
-      <c r="M52" s="20"/>
-      <c r="N52" s="17"/>
+      <c r="A52" s="18">
+        <v>46311</v>
+      </c>
+      <c r="B52" s="19">
+        <v>460</v>
+      </c>
+      <c r="C52" s="19">
+        <v>60</v>
+      </c>
+      <c r="D52" s="19">
+        <v>60</v>
+      </c>
+      <c r="E52" s="19">
+        <v>20</v>
+      </c>
+      <c r="F52" s="19">
+        <v>0</v>
+      </c>
+      <c r="G52" s="19">
+        <v>0</v>
+      </c>
+      <c r="H52" s="19">
+        <v>120</v>
+      </c>
+      <c r="I52" s="15">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J52" s="15">
+        <f t="shared" si="1"/>
+        <v>720</v>
+      </c>
+      <c r="K52" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L52" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M52" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="53" spans="1:14" ht="14.25" customHeight="1">
       <c r="A53" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>prepraing for ett</t>
+  </si>
+  <si>
+    <t>preparing for maths</t>
   </si>
 </sst>
 </file>
@@ -3328,26 +3331,50 @@
       </c>
     </row>
     <row r="53" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A53" s="18"/>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="20"/>
-      <c r="L53" s="20"/>
-      <c r="M53" s="20"/>
-      <c r="N53" s="17"/>
+      <c r="A53" s="18">
+        <v>46312</v>
+      </c>
+      <c r="B53" s="19">
+        <v>440</v>
+      </c>
+      <c r="C53" s="19">
+        <v>60</v>
+      </c>
+      <c r="D53" s="19">
+        <v>90</v>
+      </c>
+      <c r="E53" s="19">
+        <v>20</v>
+      </c>
+      <c r="F53" s="19">
+        <v>0</v>
+      </c>
+      <c r="G53" s="19">
+        <v>0</v>
+      </c>
+      <c r="H53" s="19">
+        <v>120</v>
+      </c>
+      <c r="I53" s="15">
+        <f t="shared" si="0"/>
+        <v>730</v>
+      </c>
+      <c r="J53" s="15">
+        <f t="shared" si="1"/>
+        <v>710</v>
+      </c>
+      <c r="K53" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="L53" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="M53" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="54" spans="1:14" ht="14.25" customHeight="1">
       <c r="A54" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -333,6 +333,9 @@
   </si>
   <si>
     <t>preparing for maths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">too tired </t>
   </si>
 </sst>
 </file>
@@ -3377,26 +3380,50 @@
       </c>
     </row>
     <row r="54" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A54" s="18"/>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="20"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="20"/>
-      <c r="N54" s="17"/>
+      <c r="A54" s="18">
+        <v>46313</v>
+      </c>
+      <c r="B54" s="19">
+        <v>440</v>
+      </c>
+      <c r="C54" s="19">
+        <v>90</v>
+      </c>
+      <c r="D54" s="19">
+        <v>60</v>
+      </c>
+      <c r="E54" s="19">
+        <v>30</v>
+      </c>
+      <c r="F54" s="19">
+        <v>0</v>
+      </c>
+      <c r="G54" s="19">
+        <v>0</v>
+      </c>
+      <c r="H54" s="19">
+        <v>150</v>
+      </c>
+      <c r="I54" s="15">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J54" s="15">
+        <f t="shared" si="1"/>
+        <v>670</v>
+      </c>
+      <c r="K54" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L54" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M54" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="55" spans="1:14" ht="14.25" customHeight="1">
       <c r="A55" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -336,6 +336,9 @@
   </si>
   <si>
     <t xml:space="preserve">too tired </t>
+  </si>
+  <si>
+    <t>last mid term exam</t>
   </si>
 </sst>
 </file>
@@ -3426,26 +3429,50 @@
       </c>
     </row>
     <row r="55" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A55" s="18"/>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="20"/>
-      <c r="L55" s="20"/>
-      <c r="M55" s="20"/>
-      <c r="N55" s="17"/>
+      <c r="A55" s="18">
+        <v>46314</v>
+      </c>
+      <c r="B55" s="19">
+        <v>320</v>
+      </c>
+      <c r="C55" s="19">
+        <v>30</v>
+      </c>
+      <c r="D55" s="19">
+        <v>45</v>
+      </c>
+      <c r="E55" s="19">
+        <v>20</v>
+      </c>
+      <c r="F55" s="19">
+        <v>0</v>
+      </c>
+      <c r="G55" s="19">
+        <v>0</v>
+      </c>
+      <c r="H55" s="19">
+        <v>190</v>
+      </c>
+      <c r="I55" s="15">
+        <f t="shared" si="0"/>
+        <v>605</v>
+      </c>
+      <c r="J55" s="15">
+        <f t="shared" si="1"/>
+        <v>835</v>
+      </c>
+      <c r="K55" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L55" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M55" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="56" spans="1:14" ht="14.25" customHeight="1">
       <c r="A56" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>last mid term exam</t>
+  </si>
+  <si>
+    <t>I completed 1200 m in 5:40 min</t>
   </si>
 </sst>
 </file>
@@ -3475,26 +3478,50 @@
       </c>
     </row>
     <row r="56" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A56" s="18"/>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="20"/>
-      <c r="L56" s="20"/>
-      <c r="M56" s="20"/>
-      <c r="N56" s="17"/>
+      <c r="A56" s="18">
+        <v>46315</v>
+      </c>
+      <c r="B56" s="19">
+        <v>350</v>
+      </c>
+      <c r="C56" s="19">
+        <v>45</v>
+      </c>
+      <c r="D56" s="19">
+        <v>30</v>
+      </c>
+      <c r="E56" s="19">
+        <v>20</v>
+      </c>
+      <c r="F56" s="19">
+        <v>0</v>
+      </c>
+      <c r="G56" s="19">
+        <v>0</v>
+      </c>
+      <c r="H56" s="19">
+        <v>180</v>
+      </c>
+      <c r="I56" s="15">
+        <f t="shared" si="0"/>
+        <v>625</v>
+      </c>
+      <c r="J56" s="15">
+        <f t="shared" si="1"/>
+        <v>815</v>
+      </c>
+      <c r="K56" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L56" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M56" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="57" spans="1:14" ht="14.25" customHeight="1">
       <c r="A57" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -342,6 +342,9 @@
   </si>
   <si>
     <t>I completed 1200 m in 5:40 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I'm too tired </t>
   </si>
 </sst>
 </file>
@@ -3524,26 +3527,50 @@
       </c>
     </row>
     <row r="57" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A57" s="18"/>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="20"/>
-      <c r="L57" s="20"/>
-      <c r="M57" s="20"/>
-      <c r="N57" s="17"/>
+      <c r="A57" s="18">
+        <v>46316</v>
+      </c>
+      <c r="B57" s="19">
+        <v>410</v>
+      </c>
+      <c r="C57" s="19">
+        <v>30</v>
+      </c>
+      <c r="D57" s="19">
+        <v>120</v>
+      </c>
+      <c r="E57" s="19">
+        <v>30</v>
+      </c>
+      <c r="F57" s="19">
+        <v>300</v>
+      </c>
+      <c r="G57" s="19">
+        <v>6</v>
+      </c>
+      <c r="H57" s="19">
+        <v>180</v>
+      </c>
+      <c r="I57" s="15">
+        <f t="shared" si="0"/>
+        <v>1070</v>
+      </c>
+      <c r="J57" s="15">
+        <f t="shared" si="1"/>
+        <v>370</v>
+      </c>
+      <c r="K57" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L57" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M57" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="58" spans="1:14" ht="14.25" customHeight="1">
       <c r="A58" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3573,26 +3573,50 @@
       </c>
     </row>
     <row r="58" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A58" s="18"/>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="20"/>
-      <c r="L58" s="20"/>
-      <c r="M58" s="20"/>
-      <c r="N58" s="17"/>
+      <c r="A58" s="18">
+        <v>46317</v>
+      </c>
+      <c r="B58" s="19">
+        <v>420</v>
+      </c>
+      <c r="C58" s="19">
+        <v>45</v>
+      </c>
+      <c r="D58" s="19">
+        <v>120</v>
+      </c>
+      <c r="E58" s="19">
+        <v>0</v>
+      </c>
+      <c r="F58" s="19">
+        <v>250</v>
+      </c>
+      <c r="G58" s="19">
+        <v>5</v>
+      </c>
+      <c r="H58" s="19">
+        <v>45</v>
+      </c>
+      <c r="I58" s="15">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J58" s="15">
+        <f t="shared" si="1"/>
+        <v>560</v>
+      </c>
+      <c r="K58" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L58" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M58" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="59" spans="1:14" ht="14.25" customHeight="1">
       <c r="A59" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3619,26 +3619,50 @@
       </c>
     </row>
     <row r="59" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A59" s="18"/>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="20"/>
-      <c r="L59" s="20"/>
-      <c r="M59" s="20"/>
-      <c r="N59" s="17"/>
+      <c r="A59" s="18">
+        <v>46319</v>
+      </c>
+      <c r="B59" s="19">
+        <v>460</v>
+      </c>
+      <c r="C59" s="19">
+        <v>30</v>
+      </c>
+      <c r="D59" s="19">
+        <v>60</v>
+      </c>
+      <c r="E59" s="19">
+        <v>25</v>
+      </c>
+      <c r="F59" s="19">
+        <v>0</v>
+      </c>
+      <c r="G59" s="19">
+        <v>0</v>
+      </c>
+      <c r="H59" s="19">
+        <v>120</v>
+      </c>
+      <c r="I59" s="15">
+        <f t="shared" si="0"/>
+        <v>695</v>
+      </c>
+      <c r="J59" s="15">
+        <f t="shared" si="1"/>
+        <v>745</v>
+      </c>
+      <c r="K59" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L59" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M59" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="60" spans="1:14" ht="14.25" customHeight="1">
       <c r="A60" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t xml:space="preserve">I'm too tired </t>
+  </si>
+  <si>
+    <t>tired</t>
   </si>
 </sst>
 </file>
@@ -3665,26 +3668,50 @@
       </c>
     </row>
     <row r="60" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A60" s="18"/>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="20"/>
-      <c r="L60" s="20"/>
-      <c r="M60" s="20"/>
-      <c r="N60" s="17"/>
+      <c r="A60" s="18">
+        <v>46320</v>
+      </c>
+      <c r="B60" s="19">
+        <v>420</v>
+      </c>
+      <c r="C60" s="19">
+        <v>0</v>
+      </c>
+      <c r="D60" s="19">
+        <v>120</v>
+      </c>
+      <c r="E60" s="19">
+        <v>30</v>
+      </c>
+      <c r="F60" s="19">
+        <v>0</v>
+      </c>
+      <c r="G60" s="19">
+        <v>0</v>
+      </c>
+      <c r="H60" s="19">
+        <v>150</v>
+      </c>
+      <c r="I60" s="15">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J60" s="15">
+        <f t="shared" si="1"/>
+        <v>720</v>
+      </c>
+      <c r="K60" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L60" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M60" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="61" spans="1:14" ht="14.25" customHeight="1">
       <c r="A61" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t>tired</t>
+  </si>
+  <si>
+    <t>another normal day</t>
   </si>
 </sst>
 </file>
@@ -3714,26 +3717,50 @@
       </c>
     </row>
     <row r="61" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A61" s="18"/>
-      <c r="B61" s="19"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="20"/>
-      <c r="L61" s="20"/>
-      <c r="M61" s="20"/>
-      <c r="N61" s="17"/>
+      <c r="A61" s="18">
+        <v>46321</v>
+      </c>
+      <c r="B61" s="19">
+        <v>450</v>
+      </c>
+      <c r="C61" s="19">
+        <v>30</v>
+      </c>
+      <c r="D61" s="19">
+        <v>120</v>
+      </c>
+      <c r="E61" s="19">
+        <v>50</v>
+      </c>
+      <c r="F61" s="19">
+        <v>0</v>
+      </c>
+      <c r="G61" s="19">
+        <v>0</v>
+      </c>
+      <c r="H61" s="19">
+        <v>120</v>
+      </c>
+      <c r="I61" s="15">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J61" s="15">
+        <f t="shared" si="1"/>
+        <v>670</v>
+      </c>
+      <c r="K61" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="L61" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="M61" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="62" spans="1:14" ht="14.25" customHeight="1">
       <c r="A62" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>another normal day</t>
+  </si>
+  <si>
+    <t>preparing for end term exam</t>
   </si>
 </sst>
 </file>
@@ -3763,26 +3766,50 @@
       </c>
     </row>
     <row r="62" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A62" s="18"/>
-      <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="20"/>
-      <c r="L62" s="20"/>
-      <c r="M62" s="20"/>
-      <c r="N62" s="17"/>
+      <c r="A62" s="18">
+        <v>46323</v>
+      </c>
+      <c r="B62" s="19">
+        <v>420</v>
+      </c>
+      <c r="C62" s="19">
+        <v>20</v>
+      </c>
+      <c r="D62" s="19">
+        <v>120</v>
+      </c>
+      <c r="E62" s="19">
+        <v>20</v>
+      </c>
+      <c r="F62" s="19">
+        <v>250</v>
+      </c>
+      <c r="G62" s="19">
+        <v>5</v>
+      </c>
+      <c r="H62" s="19">
+        <v>130</v>
+      </c>
+      <c r="I62" s="15">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J62" s="15">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="K62" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="L62" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="M62" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="63" spans="1:14" ht="14.25" customHeight="1">
       <c r="A63" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -354,6 +354,9 @@
   </si>
   <si>
     <t>preparing for end term exam</t>
+  </si>
+  <si>
+    <t>today was half day in uni</t>
   </si>
 </sst>
 </file>
@@ -3812,26 +3815,50 @@
       </c>
     </row>
     <row r="63" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A63" s="18"/>
-      <c r="B63" s="19"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="20"/>
-      <c r="L63" s="20"/>
-      <c r="M63" s="20"/>
-      <c r="N63" s="17"/>
+      <c r="A63" s="18">
+        <v>46324</v>
+      </c>
+      <c r="B63" s="19">
+        <v>440</v>
+      </c>
+      <c r="C63" s="19">
+        <v>30</v>
+      </c>
+      <c r="D63" s="19">
+        <v>120</v>
+      </c>
+      <c r="E63" s="19">
+        <v>0</v>
+      </c>
+      <c r="F63" s="19">
+        <v>200</v>
+      </c>
+      <c r="G63" s="19">
+        <v>4</v>
+      </c>
+      <c r="H63" s="19">
+        <v>150</v>
+      </c>
+      <c r="I63" s="15">
+        <f t="shared" si="0"/>
+        <v>940</v>
+      </c>
+      <c r="J63" s="15">
+        <f t="shared" si="1"/>
+        <v>500</v>
+      </c>
+      <c r="K63" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="L63" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="M63" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="64" spans="1:14" ht="14.25" customHeight="1">
       <c r="A64" s="18"/>

--- a/12622534.xlsx
+++ b/12622534.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3861,26 +3861,50 @@
       </c>
     </row>
     <row r="64" spans="1:14" ht="14.25" customHeight="1">
-      <c r="A64" s="18"/>
-      <c r="B64" s="19"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="20"/>
-      <c r="L64" s="20"/>
-      <c r="M64" s="20"/>
-      <c r="N64" s="17"/>
+      <c r="A64" s="18">
+        <v>46325</v>
+      </c>
+      <c r="B64" s="19">
+        <v>420</v>
+      </c>
+      <c r="C64" s="19">
+        <v>0</v>
+      </c>
+      <c r="D64" s="19">
+        <v>120</v>
+      </c>
+      <c r="E64" s="19">
+        <v>20</v>
+      </c>
+      <c r="F64" s="19">
+        <v>200</v>
+      </c>
+      <c r="G64" s="19">
+        <v>4</v>
+      </c>
+      <c r="H64" s="19">
+        <v>120</v>
+      </c>
+      <c r="I64" s="15">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J64" s="15">
+        <f t="shared" si="1"/>
+        <v>560</v>
+      </c>
+      <c r="K64" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="L64" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="M64" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="65" spans="1:14" ht="14.25" customHeight="1">
       <c r="A65" s="18"/>
